--- a/site/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/site/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/site/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/site/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/site/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008120</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005210</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008640</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003110</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002190</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005780</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-012874</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001420</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004812</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004110</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003450</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-008912</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-014289</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001890</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002840</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001955</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004550</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham</t>
+          <t>https://www.nccourts.gov/locations/durham?docket=2024-NC-002100</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001501</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009041</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001248</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004990</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009188</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001622</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001844</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/site/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/site/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008120</t>
+          <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005210</t>
+          <t>https://www.sdttc.com/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008640</t>
+          <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003110</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002190</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005780</t>
+          <t>https://www.sdttc.com/</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
+          <t>https://www.cobbtax.org/</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-012874</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001420</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004812</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004110</t>
+          <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003450</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-008912</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-014289</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001890</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002840</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
+          <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001955</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004550</t>
+          <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
+          <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham?docket=2024-NC-002100</t>
+          <t>https://www.nccourts.gov/locations/durham</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001501</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009041</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001248</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004990</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009188</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001622</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001844</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/site/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/site/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/notice-of-excess-proceeds/?docket=2024-CA-008120</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/property-tax-sales.html?docket=2024-CA-005210</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/notice-of-excess-proceeds/?docket=2024-CA-008640</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg-county?docket=2024-NC-003110</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/cases/public-records-search/?docket=2024-TN-002190</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/property-tax-sales.html?docket=2024-CA-005780</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/property/tax_sale/index.php?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/QOS/default.aspx?caseNumber=2024-CA-012874</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake-county?docket=2024-NC-001420</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/property-tax-deeds.page?caseNumber=2024-TD-004812</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://www.shelbycountytn.gov/222/Chancery-Court?docket=2024-TN-004110</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg-county?docket=2024-NC-003450</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-008912</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/QOS/default.aspx?caseNumber=2024-CA-014289</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake-county?docket=2024-NC-001890</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/cases/public-records-search/?docket=2024-TN-002840</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001955</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://www.shelbycountytn.gov/222/Chancery-Court?docket=2024-TN-004550</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/property-tax/tax-sale-excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham</t>
+          <t>https://www.nccourts.gov/locations/durham-county?docket=2024-NC-002100</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001501</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-009041</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001248</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/property-tax-deeds.page?caseNumber=2024-TD-004990</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-009188</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001622</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001844</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/site/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/site/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/site/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/site/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/site/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/site/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/site/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/site/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/site/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/site/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/site/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/site/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
